--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Baran/excel/Baran_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Baran/excel/Baran_Survey_Analysis_Master.xlsx
@@ -148,19 +148,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
       <c r="T3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="U3" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       <c r="T4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="U4" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -931,7 +931,7 @@
       <c r="T5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
       <c r="T6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="6" t="n">
+      <c r="U6" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
           <t>Electric goods</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
@@ -1061,7 +1061,7 @@
       <c r="T7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
           <t>Stone shop</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
@@ -1126,7 +1126,7 @@
       <c r="T8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="U8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
           <t>Agri-input retail,</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
@@ -1191,7 +1191,7 @@
       <c r="T9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="U9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
           <t>AI/breeding kits</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
@@ -1256,7 +1256,7 @@
       <c r="T10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="U10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
           <t>Goat trading</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="7" t="n">
@@ -1321,91 +1321,91 @@
       <c r="T11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Trading TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>TOTAL TRADING</t>
         </is>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <f>SUM(D3:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <f>SUM(E3:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <f>IF(D12&gt;0, E12/D12, 0)</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <f>SUM(G3:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="12">
         <f>SUM(H3:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="12">
         <f>SUM(I3:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="12">
         <f>SUM(J3:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="12">
         <f>SUM(K3:K11)</f>
         <v/>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="12">
         <f>SUM(L3:L11)</f>
         <v/>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="12">
         <f>SUM(M3:M11)</f>
         <v/>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="12">
         <f>SUM(N3:N11)</f>
         <v/>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="12">
         <f>SUM(O3:O11)</f>
         <v/>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="12">
         <f>SUM(P3:P11)</f>
         <v/>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="12">
         <f>SUM(Q3:Q11)</f>
         <v/>
       </c>
-      <c r="R12" s="11">
+      <c r="R12" s="12">
         <f>SUM(R3:R11)</f>
         <v/>
       </c>
-      <c r="S12" s="11">
+      <c r="S12" s="12">
         <f>SUM(S3:S11)</f>
         <v/>
       </c>
-      <c r="T12" s="11">
+      <c r="T12" s="12">
         <f>SUM(T3:T11)</f>
         <v/>
       </c>
-      <c r="U12" s="10">
+      <c r="U12" s="11">
         <f>SUM(U3:U11)</f>
         <v/>
       </c>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
       <c r="T13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
           <t>Tailoring</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
@@ -1540,7 +1540,7 @@
       <c r="T14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
           <t>Beauty parlour</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
@@ -1605,7 +1605,7 @@
       <c r="T15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
           <t>Auto-mechanic/ two-wheeler repair</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
@@ -1670,7 +1670,7 @@
       <c r="T16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1684,14 +1684,14 @@
           <t>E-mitra</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>1</v>
+      <c r="D17" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>470000</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>470000</v>
+        <v>156666.6666666667</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>68000</v>
@@ -1735,7 +1735,7 @@
       <c r="T17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="n">
+      <c r="U17" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
           <t>Transport</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
@@ -1800,7 +1800,7 @@
       <c r="T18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
           <t>Tent house</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
@@ -1865,7 +1865,7 @@
       <c r="T19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
           <t>Mobile repair shop</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
@@ -1930,7 +1930,7 @@
       <c r="T20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
           <t>Stone cutting</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
@@ -1995,91 +1995,91 @@
       <c r="T21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Service TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>TOTAL SERVICE</t>
         </is>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="11">
         <f>SUM(D13:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <f>SUM(E13:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <f>IF(D22&gt;0, E22/D22, 0)</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <f>SUM(G13:G21)</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <f>SUM(H13:H21)</f>
         <v/>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="12">
         <f>SUM(I13:I21)</f>
         <v/>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <f>SUM(J13:J21)</f>
         <v/>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <f>SUM(K13:K21)</f>
         <v/>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <f>SUM(L13:L21)</f>
         <v/>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="12">
         <f>SUM(M13:M21)</f>
         <v/>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="12">
         <f>SUM(N13:N21)</f>
         <v/>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="12">
         <f>SUM(O13:O21)</f>
         <v/>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="12">
         <f>SUM(P13:P21)</f>
         <v/>
       </c>
-      <c r="Q22" s="11">
+      <c r="Q22" s="12">
         <f>SUM(Q13:Q21)</f>
         <v/>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="12">
         <f>SUM(R13:R21)</f>
         <v/>
       </c>
-      <c r="S22" s="11">
+      <c r="S22" s="12">
         <f>SUM(S13:S21)</f>
         <v/>
       </c>
-      <c r="T22" s="11">
+      <c r="T22" s="12">
         <f>SUM(T13:T21)</f>
         <v/>
       </c>
-      <c r="U22" s="10">
+      <c r="U22" s="11">
         <f>SUM(U13:U21)</f>
         <v/>
       </c>
@@ -2098,7 +2098,7 @@
           <t>Sanitary napkin making</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
@@ -2149,7 +2149,7 @@
       <c r="T23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
       <c r="T24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
       <c r="T25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
           <t>Juice</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
@@ -2344,7 +2344,7 @@
       <c r="T26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
           <t>Food processing (pickle/badi/papad making)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="7" t="n">
@@ -2409,7 +2409,7 @@
       <c r="T27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
       <c r="T28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
           <t>Sweet box making</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
@@ -2539,7 +2539,7 @@
       <c r="T29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
           <t>Flag making</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
@@ -2604,7 +2604,7 @@
       <c r="T30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="U30" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
           <t>Leather products</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="n">
@@ -2669,7 +2669,7 @@
       <c r="T31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U31" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
           <t>Stone idols</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
@@ -2734,7 +2734,7 @@
       <c r="T32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="U32" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
           <t>Any other</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="7" t="n">
@@ -2799,91 +2799,91 @@
       <c r="T33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="U33" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Production TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>TOTAL PRODUCTION</t>
         </is>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="11">
         <f>SUM(D23:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="12">
         <f>SUM(E23:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="12">
         <f>IF(D34&gt;0, E34/D34, 0)</f>
         <v/>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="12">
         <f>SUM(G23:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="12">
         <f>SUM(H23:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="12">
         <f>SUM(I23:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="12">
         <f>SUM(J23:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="11">
+      <c r="K34" s="12">
         <f>SUM(K23:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="11">
+      <c r="L34" s="12">
         <f>SUM(L23:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="11">
+      <c r="M34" s="12">
         <f>SUM(M23:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="11">
+      <c r="N34" s="12">
         <f>SUM(N23:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="11">
+      <c r="O34" s="12">
         <f>SUM(O23:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="11">
+      <c r="P34" s="12">
         <f>SUM(P23:P33)</f>
         <v/>
       </c>
-      <c r="Q34" s="11">
+      <c r="Q34" s="12">
         <f>SUM(Q23:Q33)</f>
         <v/>
       </c>
-      <c r="R34" s="11">
+      <c r="R34" s="12">
         <f>SUM(R23:R33)</f>
         <v/>
       </c>
-      <c r="S34" s="11">
+      <c r="S34" s="12">
         <f>SUM(S23:S33)</f>
         <v/>
       </c>
-      <c r="T34" s="11">
+      <c r="T34" s="12">
         <f>SUM(T23:T33)</f>
         <v/>
       </c>
-      <c r="U34" s="10">
+      <c r="U34" s="11">
         <f>SUM(U23:U33)</f>
         <v/>
       </c>
@@ -3856,20 +3856,20 @@
           <t>Vegetable/Fruit</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3882,20 +3882,20 @@
           <t>Grocery</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3908,20 +3908,20 @@
           <t>Fancy/Cosmetic/General store</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3934,20 +3934,20 @@
           <t>Apparel/fabric</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3960,19 +3960,19 @@
           <t>Electric goods</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3986,19 +3986,19 @@
           <t>Stone shop</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4012,19 +4012,19 @@
           <t>Agri-input retail,</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4038,19 +4038,19 @@
           <t>AI/breeding kits</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4064,30 +4064,30 @@
           <t>Goat trading</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Trading TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>TOTAL TRADING</t>
         </is>
@@ -4127,20 +4127,20 @@
           <t>Flour mill</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4153,19 +4153,19 @@
           <t>Tailoring</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="D15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4179,19 +4179,19 @@
           <t>Beauty parlour</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4205,19 +4205,19 @@
           <t>Auto-mechanic/ two-wheeler repair</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n">
+      <c r="D17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4231,20 +4231,20 @@
           <t>E-mitra</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>1</v>
+      <c r="G18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -4257,19 +4257,19 @@
           <t>Transport</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
+      <c r="D19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4283,19 +4283,19 @@
           <t>Tent house</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
+      <c r="D20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4309,19 +4309,19 @@
           <t>Mobile repair shop</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="D21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4335,30 +4335,30 @@
           <t>Stone cutting</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="D22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Service TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>TOTAL SERVICE</t>
         </is>
@@ -4398,19 +4398,19 @@
           <t>Sanitary napkin making</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="D24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4424,20 +4424,20 @@
           <t>Handicraft</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="D25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4451,19 +4451,19 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4476,19 +4476,19 @@
           <t>Juice</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
+      <c r="D27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4502,19 +4502,19 @@
           <t>Food processing (pickle/badi/papad making)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="n">
+      <c r="D28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4528,20 +4528,20 @@
           <t>Food making (Sweets/Namkeen/hotel)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="n">
+      <c r="D29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4554,19 +4554,19 @@
           <t>Sweet box making</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="n">
+      <c r="D30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4580,19 +4580,19 @@
           <t>Flag making</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
+      <c r="D31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4606,19 +4606,19 @@
           <t>Leather products</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
+      <c r="D32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4632,19 +4632,19 @@
           <t>Stone idols</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
+      <c r="D33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4658,30 +4658,30 @@
           <t>Any other</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
+      <c r="D34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Production TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>TOTAL PRODUCTION</t>
         </is>
@@ -4800,11 +4800,11 @@
           <t>I need help from my family in running my enterprise more effectively</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
-        <v>1</v>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>1</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="5">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="6">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="8">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="9">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="14">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="16">
@@ -4943,7 +4943,7 @@
           <t>OSF/SVEP CRP helps in sourcing material</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="25" t="n">
@@ -4956,7 +4956,7 @@
           <t>I want to source material from different places but I need support</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="25" t="n">
@@ -4969,11 +4969,11 @@
           <t>I am content to source material from nearby market</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>1</v>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="19">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C2" s="27" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3"/>
@@ -5062,11 +5062,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>1</v>
+      <c r="C5" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -5126,11 +5126,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>1</v>
+      <c r="C10" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="11">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="12">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="16">
@@ -5203,11 +5203,11 @@
           <t>In Service</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>1</v>
+      <c r="C16" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="18">
@@ -5267,8 +5267,8 @@
           <t>PAN card</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>1</v>
+      <c r="C21" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="D21" s="25" t="n">
         <v>1</v>
@@ -5280,8 +5280,8 @@
           <t>Aadhar card</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
-        <v>1</v>
+      <c r="C22" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="D22" s="25" t="n">
         <v>1</v>
@@ -5293,11 +5293,11 @@
           <t>Udyam Aadhar</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
-        <v>1</v>
+      <c r="C23" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="24">
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="25">
@@ -5319,7 +5319,7 @@
           <t>FSSAI</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="25" t="n">
@@ -5332,11 +5332,11 @@
           <t>Caste certificate</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>1</v>
+      <c r="C26" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="27">
@@ -5345,11 +5345,11 @@
           <t>Income certificate</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>1</v>
+      <c r="C27" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="28">
@@ -5396,7 +5396,7 @@
           <t>18-25</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="25" t="n">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="33">
@@ -5422,11 +5422,11 @@
           <t>36-45</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>1</v>
+      <c r="C33" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="34">
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="35">
@@ -5448,7 +5448,7 @@
           <t>Above 55</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="C35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="25" t="n">
@@ -5499,7 +5499,7 @@
           <t>Single</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="25" t="n">
@@ -5512,8 +5512,8 @@
           <t>Married</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>1</v>
+      <c r="C40" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="D40" s="25" t="n">
         <v>1</v>
@@ -5525,7 +5525,7 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="25" t="n">
@@ -5538,7 +5538,7 @@
           <t>Separated</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n">
+      <c r="C42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="25" t="n">
@@ -5551,7 +5551,7 @@
           <t>Divorced</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="25" t="n">
@@ -5602,11 +5602,11 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>1</v>
+      <c r="C47" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="48">
@@ -5615,7 +5615,7 @@
           <t>ST</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="25" t="n">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="55">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="56">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="57">
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="58">
@@ -5744,7 +5744,7 @@
           <t>Upto 10th</t>
         </is>
       </c>
-      <c r="C58" s="6" t="n">
+      <c r="C58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="25" t="n">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="60">
@@ -5770,7 +5770,7 @@
           <t>Diploma</t>
         </is>
       </c>
-      <c r="C60" s="6" t="n">
+      <c r="C60" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="25" t="n">
@@ -5783,11 +5783,11 @@
           <t>Graduate</t>
         </is>
       </c>
-      <c r="C61" s="12" t="n">
-        <v>1</v>
+      <c r="C61" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="62">
@@ -5796,7 +5796,7 @@
           <t>B.Ed</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="25" t="n">
@@ -5847,11 +5847,11 @@
           <t>Upto 4</t>
         </is>
       </c>
-      <c r="C66" s="12" t="n">
-        <v>1</v>
+      <c r="C66" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>1</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="67">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="68">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="69">
@@ -5886,7 +5886,7 @@
           <t>8-10</t>
         </is>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="25" t="n">
@@ -5899,7 +5899,7 @@
           <t>More than 10</t>
         </is>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C70" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="25" t="n">
@@ -5950,7 +5950,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C74" s="6" t="n">
+      <c r="C74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="25" t="n">
@@ -5963,11 +5963,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C75" s="12" t="n">
-        <v>1</v>
+      <c r="C75" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="76">
@@ -5976,7 +5976,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="25" t="n">
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="78">
@@ -6002,7 +6002,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C78" s="6" t="n">
+      <c r="C78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="25" t="n">
@@ -6015,7 +6015,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C79" s="6" t="n">
+      <c r="C79" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="25" t="n">
@@ -6028,7 +6028,7 @@
           <t>More than 6</t>
         </is>
       </c>
-      <c r="C80" s="6" t="n">
+      <c r="C80" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="25" t="n">
@@ -6079,7 +6079,7 @@
           <t>Less than Rs 80,000</t>
         </is>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C84" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="25" t="n">
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="86">
@@ -6105,7 +6105,7 @@
           <t>Rs 1,20,001 to Rs 1,60,000</t>
         </is>
       </c>
-      <c r="C86" s="6" t="n">
+      <c r="C86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="25" t="n">
@@ -6118,11 +6118,11 @@
           <t>Rs 1,60,001 to Rs 2,00,000</t>
         </is>
       </c>
-      <c r="C87" s="12" t="n">
-        <v>1</v>
+      <c r="C87" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="88">
@@ -6131,7 +6131,7 @@
           <t>Rs 2,00,001 to Rs 2,40,000</t>
         </is>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C88" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="25" t="n">
@@ -6144,7 +6144,7 @@
           <t>Rs 2,40,001 to Rs 2,80,000</t>
         </is>
       </c>
-      <c r="C89" s="6" t="n">
+      <c r="C89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="25" t="n">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="91">
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="92">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="93">
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="94">
@@ -6247,11 +6247,11 @@
           <t>Own Savings</t>
         </is>
       </c>
-      <c r="C97" s="12" t="n">
+      <c r="C97" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="98">
@@ -6260,7 +6260,7 @@
           <t>Financed by family member</t>
         </is>
       </c>
-      <c r="C98" s="6" t="n">
+      <c r="C98" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D98" s="25" t="n">
@@ -6273,11 +6273,11 @@
           <t>Profit from business</t>
         </is>
       </c>
-      <c r="C99" s="12" t="n">
+      <c r="C99" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="100">
@@ -6286,7 +6286,7 @@
           <t>Mortgaged gold/silver</t>
         </is>
       </c>
-      <c r="C100" s="6" t="n">
+      <c r="C100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D100" s="25" t="n">
@@ -6299,7 +6299,7 @@
           <t>Sold gold/silver</t>
         </is>
       </c>
-      <c r="C101" s="6" t="n">
+      <c r="C101" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="25" t="n">
@@ -6312,7 +6312,7 @@
           <t>Loan from family</t>
         </is>
       </c>
-      <c r="C102" s="6" t="n">
+      <c r="C102" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D102" s="25" t="n">
@@ -6325,7 +6325,7 @@
           <t>Moneylender</t>
         </is>
       </c>
-      <c r="C103" s="6" t="n">
+      <c r="C103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D103" s="25" t="n">
@@ -6338,11 +6338,11 @@
           <t>SHG</t>
         </is>
       </c>
-      <c r="C104" s="12" t="n">
+      <c r="C104" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="105">
@@ -6351,11 +6351,11 @@
           <t>OSF/SVEP</t>
         </is>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C105" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="106">
@@ -6364,11 +6364,11 @@
           <t>Subsidy/grant</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C106" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="107">
@@ -6377,7 +6377,7 @@
           <t>Private saving groups/BC</t>
         </is>
       </c>
-      <c r="C107" s="6" t="n">
+      <c r="C107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="25" t="n">
@@ -6390,7 +6390,7 @@
           <t>NBFC</t>
         </is>
       </c>
-      <c r="C108" s="6" t="n">
+      <c r="C108" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="25" t="n">
@@ -6403,7 +6403,7 @@
           <t>Mudra loan</t>
         </is>
       </c>
-      <c r="C109" s="6" t="n">
+      <c r="C109" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D109" s="25" t="n">
@@ -6416,7 +6416,7 @@
           <t>Banks</t>
         </is>
       </c>
-      <c r="C110" s="6" t="n">
+      <c r="C110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D110" s="25" t="n">
@@ -6467,11 +6467,11 @@
           <t>Seed capital to buy material and set up the shop</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C114" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="115">
@@ -6480,11 +6480,11 @@
           <t>Buy new machine to increase the production capacity ( eg: sewing machine)</t>
         </is>
       </c>
-      <c r="C115" s="12" t="n">
+      <c r="C115" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="116">
@@ -6493,7 +6493,7 @@
           <t>Buy assets to store and sell new products ( eg: fridge)</t>
         </is>
       </c>
-      <c r="C116" s="6" t="n">
+      <c r="C116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="25" t="n">
@@ -6506,7 +6506,7 @@
           <t>Get additional space to expand my business ( eg: addition of flour mill)</t>
         </is>
       </c>
-      <c r="C117" s="6" t="n">
+      <c r="C117" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D117" s="25" t="n">
@@ -6519,7 +6519,7 @@
           <t>Buy more material to increase the product range offered (eg: clothes in a fancy store)</t>
         </is>
       </c>
-      <c r="C118" s="6" t="n">
+      <c r="C118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D118" s="25" t="n">
@@ -6532,7 +6532,7 @@
           <t>Buy more material/inputs to increase scale of business/production</t>
         </is>
       </c>
-      <c r="C119" s="6" t="n">
+      <c r="C119" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D119" s="25" t="n">
@@ -6545,7 +6545,7 @@
           <t>Buy vehicle to access new market to buy/sell goods</t>
         </is>
       </c>
-      <c r="C120" s="6" t="n">
+      <c r="C120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D120" s="25" t="n">
@@ -6558,7 +6558,7 @@
           <t>Access better transport services to access new market to buy/sell goods</t>
         </is>
       </c>
-      <c r="C121" s="6" t="n">
+      <c r="C121" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D121" s="25" t="n">
@@ -6571,7 +6571,7 @@
           <t>Buy mobile phone to promote/sell my goods online</t>
         </is>
       </c>
-      <c r="C122" s="6" t="n">
+      <c r="C122" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D122" s="25" t="n">
@@ -6584,7 +6584,7 @@
           <t>Any other, specify……….</t>
         </is>
       </c>
-      <c r="C123" s="6" t="n">
+      <c r="C123" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="25" t="n">
@@ -6597,11 +6597,11 @@
           <t>Not used the source</t>
         </is>
       </c>
-      <c r="C124" s="12" t="n">
+      <c r="C124" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="125">
@@ -6649,10 +6649,10 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="129">
@@ -6661,11 +6661,11 @@
           <t>I regularly plough in my business earnings</t>
         </is>
       </c>
-      <c r="C129" s="12" t="n">
-        <v>1</v>
+      <c r="C129" s="6" t="n">
+        <v>13</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>1</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="130">
@@ -6674,11 +6674,11 @@
           <t>SHG loan size is smaller than my requirement</t>
         </is>
       </c>
-      <c r="C130" s="12" t="n">
-        <v>1</v>
+      <c r="C130" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>1</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="131">
@@ -6687,7 +6687,7 @@
           <t>I get the required loan easily from the moneylender/NBFIs.</t>
         </is>
       </c>
-      <c r="C131" s="6" t="n">
+      <c r="C131" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D131" s="25" t="n">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D132" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="133">
@@ -6713,7 +6713,7 @@
           <t>I don't prefer money lender or NBFIs as the interest rate is high</t>
         </is>
       </c>
-      <c r="C133" s="6" t="n">
+      <c r="C133" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D133" s="25" t="n">
@@ -6726,7 +6726,7 @@
           <t>I don't prefer money lender or NBFIs as the repayment time is shorter for my convenience</t>
         </is>
       </c>
-      <c r="C134" s="6" t="n">
+      <c r="C134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="25" t="n">
@@ -6777,11 +6777,11 @@
           <t>I don’t need to ask money from my husband/family for my needs.</t>
         </is>
       </c>
-      <c r="C138" s="12" t="n">
-        <v>1</v>
+      <c r="C138" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D138" s="25" t="n">
-        <v>1</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="139">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="C139" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D139" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="140">
@@ -6803,11 +6803,11 @@
           <t>The income from enterprise is used in covering education related expenses for my children.</t>
         </is>
       </c>
-      <c r="C140" s="12" t="n">
-        <v>1</v>
+      <c r="C140" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="141">
@@ -6816,11 +6816,11 @@
           <t>I have been able to pay the family debts.</t>
         </is>
       </c>
-      <c r="C141" s="12" t="n">
-        <v>1</v>
+      <c r="C141" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="142">
@@ -6829,11 +6829,11 @@
           <t xml:space="preserve">I have contributed money in acquiring assets for my family </t>
         </is>
       </c>
-      <c r="C142" s="12" t="n">
-        <v>1</v>
+      <c r="C142" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="143">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="144">
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="145">
@@ -6906,11 +6906,11 @@
           <t>Upto Rs 1,00,000</t>
         </is>
       </c>
-      <c r="C148" s="12" t="n">
-        <v>1</v>
+      <c r="C148" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
@@ -6920,10 +6920,10 @@
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="150">
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="151">
@@ -6945,7 +6945,7 @@
           <t>Rs 5,00,001-Rs 7,00,000</t>
         </is>
       </c>
-      <c r="C151" s="6" t="n">
+      <c r="C151" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D151" s="25" t="n">
@@ -6958,7 +6958,7 @@
           <t>Rs 7,00,001-Rs 9,00,000</t>
         </is>
       </c>
-      <c r="C152" s="6" t="n">
+      <c r="C152" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D152" s="25" t="n">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="154">
@@ -7022,11 +7022,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C157" s="12" t="n">
-        <v>1</v>
+      <c r="C157" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D157" s="25" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="158">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D158" s="25" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="159">
@@ -7086,11 +7086,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C162" s="12" t="n">
+      <c r="C162" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D162" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="163">
@@ -7100,10 +7100,10 @@
         </is>
       </c>
       <c r="C163" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="164">
@@ -7150,7 +7150,7 @@
           <t>Upto Rs 2000</t>
         </is>
       </c>
-      <c r="C167" s="6" t="n">
+      <c r="C167" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D167" s="25" t="n">
@@ -7163,7 +7163,7 @@
           <t>Rs 2000 to Rs 3000</t>
         </is>
       </c>
-      <c r="C168" s="6" t="n">
+      <c r="C168" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D168" s="25" t="n">
@@ -7176,7 +7176,7 @@
           <t>Rs 3000 to Rs 4000</t>
         </is>
       </c>
-      <c r="C169" s="6" t="n">
+      <c r="C169" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D169" s="25" t="n">
@@ -7189,7 +7189,7 @@
           <t>Rs 4000 to Rs 5000</t>
         </is>
       </c>
-      <c r="C170" s="6" t="n">
+      <c r="C170" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D170" s="25" t="n">
@@ -7202,7 +7202,7 @@
           <t>Rs 5000 to Rs 6000</t>
         </is>
       </c>
-      <c r="C171" s="6" t="n">
+      <c r="C171" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D171" s="25" t="n">
@@ -7215,11 +7215,11 @@
           <t>Above Rs 6000</t>
         </is>
       </c>
-      <c r="C172" s="12" t="n">
-        <v>1</v>
+      <c r="C172" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="D172" s="25" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="173">
@@ -7228,7 +7228,7 @@
           <t>Cant say</t>
         </is>
       </c>
-      <c r="C173" s="6" t="n">
+      <c r="C173" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D173" s="25" t="n">
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="C177" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D177" s="25" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="178">
@@ -7292,11 +7292,11 @@
           <t>Getting necessary documents (Aadhar/PAN/Udyam/FSSAI)</t>
         </is>
       </c>
-      <c r="C178" s="12" t="n">
-        <v>1</v>
+      <c r="C178" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="D178" s="25" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="179">
@@ -7305,11 +7305,11 @@
           <t>They helped us to understand business plans</t>
         </is>
       </c>
-      <c r="C179" s="12" t="n">
-        <v>1</v>
+      <c r="C179" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D179" s="25" t="n">
-        <v>1</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="180">
@@ -7318,11 +7318,11 @@
           <t>They gave us new ideas to improve our profit.</t>
         </is>
       </c>
-      <c r="C180" s="12" t="n">
-        <v>1</v>
+      <c r="C180" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D180" s="25" t="n">
-        <v>1</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="181">
@@ -7331,11 +7331,11 @@
           <t>They trained us on maintaining records which we didn’t know earlier</t>
         </is>
       </c>
-      <c r="C181" s="12" t="n">
-        <v>1</v>
+      <c r="C181" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="D181" s="25" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="182">
@@ -7344,11 +7344,11 @@
           <t>They helped in accessing loans from bank</t>
         </is>
       </c>
-      <c r="C182" s="12" t="n">
-        <v>1</v>
+      <c r="C182" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D182" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="183">
@@ -7357,11 +7357,11 @@
           <t>They helped in our communication skills</t>
         </is>
       </c>
-      <c r="C183" s="12" t="n">
-        <v>1</v>
+      <c r="C183" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D183" s="25" t="n">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="184">
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="C184" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D184" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="185">
@@ -7383,7 +7383,7 @@
           <t>They helped in learning use of instagram</t>
         </is>
       </c>
-      <c r="C185" s="6" t="n">
+      <c r="C185" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D185" s="25" t="n">
@@ -7396,7 +7396,7 @@
           <t>They helped us to understand our competitors and suggested ways to beat the competition</t>
         </is>
       </c>
-      <c r="C186" s="6" t="n">
+      <c r="C186" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D186" s="25" t="n">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="C190" s="6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D190" s="25" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="191">
@@ -7460,11 +7460,11 @@
           <t>Need help in accessing Mudra loan</t>
         </is>
       </c>
-      <c r="C191" s="12" t="n">
-        <v>1</v>
+      <c r="C191" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="D191" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="192">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="C192" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D192" s="25" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="193">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="C193" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D193" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="194">
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="C194" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D194" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="195">
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="C195" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D195" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="196">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="C196" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="197">
@@ -7539,10 +7539,10 @@
         </is>
       </c>
       <c r="C197" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D197" s="25" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="198">
@@ -7589,11 +7589,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C201" s="12" t="n">
-        <v>1</v>
+      <c r="C201" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D201" s="25" t="n">
-        <v>1</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="202">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="C202" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D202" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="203">
@@ -7616,10 +7616,10 @@
         </is>
       </c>
       <c r="C203" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D203" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="204">
@@ -7666,11 +7666,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C207" s="12" t="n">
-        <v>1</v>
+      <c r="C207" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="D207" s="25" t="n">
-        <v>1</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="208">
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="C208" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D208" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="209">
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="C212" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D212" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="213">
@@ -7743,11 +7743,11 @@
           <t>5-10</t>
         </is>
       </c>
-      <c r="C213" s="12" t="n">
-        <v>1</v>
+      <c r="C213" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D213" s="25" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="214">
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="C214" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D214" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="215">
@@ -7769,7 +7769,7 @@
           <t>20-40</t>
         </is>
       </c>
-      <c r="C215" s="6" t="n">
+      <c r="C215" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D215" s="25" t="n">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="C216" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D216" s="25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="217">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="C220" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D220" s="25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="221">
@@ -7846,11 +7846,11 @@
           <t>I regularly share images/reels on instagram to get orders</t>
         </is>
       </c>
-      <c r="C221" s="12" t="n">
+      <c r="C221" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D221" s="25" t="n">
-        <v>1</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="222">
@@ -7859,7 +7859,7 @@
           <t>It is important but I don’t have access to smart phone</t>
         </is>
       </c>
-      <c r="C222" s="6" t="n">
+      <c r="C222" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D222" s="25" t="n">
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="C223" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D223" s="25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="224">
@@ -7885,7 +7885,7 @@
           <t>I don't have time to learn and use social media</t>
         </is>
       </c>
-      <c r="C224" s="6" t="n">
+      <c r="C224" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D224" s="25" t="n">
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="C225" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D225" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="226">
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="C226" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D226" s="25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="227">
@@ -7962,11 +7962,11 @@
           <t>Whatsapp</t>
         </is>
       </c>
-      <c r="C230" s="12" t="n">
-        <v>1</v>
+      <c r="C230" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="D230" s="25" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="231">
@@ -7975,11 +7975,11 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C231" s="12" t="n">
-        <v>1</v>
+      <c r="C231" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="D231" s="25" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="232">
@@ -7988,7 +7988,7 @@
           <t>Pinterest</t>
         </is>
       </c>
-      <c r="C232" s="6" t="n">
+      <c r="C232" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D232" s="25" t="n">
@@ -8001,7 +8001,7 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C233" s="6" t="n">
+      <c r="C233" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D233" s="25" t="n">
@@ -8014,7 +8014,7 @@
           <t>Snapchat</t>
         </is>
       </c>
-      <c r="C234" s="6" t="n">
+      <c r="C234" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D234" s="25" t="n">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="C235" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D235" s="25" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="236">
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="C239" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D239" s="25" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="240">
@@ -8091,11 +8091,11 @@
           <t>Share images to promote business</t>
         </is>
       </c>
-      <c r="C240" s="12" t="n">
-        <v>1</v>
+      <c r="C240" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D240" s="25" t="n">
-        <v>1</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="241">
@@ -8104,7 +8104,7 @@
           <t>Share images to enquire about the availability of products to vendors</t>
         </is>
       </c>
-      <c r="C241" s="6" t="n">
+      <c r="C241" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D241" s="25" t="n">
@@ -8117,7 +8117,7 @@
           <t>Get new ideas and information about new products/services</t>
         </is>
       </c>
-      <c r="C242" s="6" t="n">
+      <c r="C242" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D242" s="25" t="n">
@@ -8130,7 +8130,7 @@
           <t>Don’t use social media</t>
         </is>
       </c>
-      <c r="C243" s="6" t="n">
+      <c r="C243" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D243" s="25" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C247" s="32" t="inlineStr">
         <is>
-          <t>6.0 Years</t>
+          <t>4.9 Years</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>6.0 Years</t>
+          <t>4.8 Years</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C249" s="32" t="inlineStr">
         <is>
-          <t>6.0 Years</t>
+          <t>5.7 Years</t>
         </is>
       </c>
     </row>
